--- a/data/trans_dic/P26-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P26-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que tienen algún familiar que fuma habitualmente en casa</t>
+          <t>Población que tienen algún familiar que fuma habitualmente en casa (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,55; 25,05</t>
+          <t>19,47; 24,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,24; 29,37</t>
+          <t>23,54; 29,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,2; 25,75</t>
+          <t>19,24; 25,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,57; 14,96</t>
+          <t>8,75; 15,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,01; 35,66</t>
+          <t>30,07; 35,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,6; 37,44</t>
+          <t>31,95; 37,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,63; 24,06</t>
+          <t>18,25; 24,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,47; 13,64</t>
+          <t>9,43; 13,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,11; 29,9</t>
+          <t>26,06; 29,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,69; 32,78</t>
+          <t>28,72; 32,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,41; 23,46</t>
+          <t>19,54; 23,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,8; 13,39</t>
+          <t>9,76; 13,3</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,91; 35,92</t>
+          <t>30,91; 35,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,81; 39,2</t>
+          <t>34,71; 39,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,62; 29,63</t>
+          <t>25,61; 29,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,39; 43,67</t>
+          <t>11,43; 47,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,25; 45,48</t>
+          <t>40,02; 45,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,1; 46,85</t>
+          <t>41,98; 46,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,44; 32,79</t>
+          <t>28,34; 32,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,05; 16,24</t>
+          <t>9,73; 16,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,05; 39,74</t>
+          <t>36,26; 39,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38,93; 42,2</t>
+          <t>38,82; 42,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,59; 30,64</t>
+          <t>27,39; 30,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,41; 34,18</t>
+          <t>12,63; 34,38</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,95; 30,28</t>
+          <t>22,06; 29,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,06; 34,4</t>
+          <t>25,23; 34,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 24,65</t>
+          <t>16,5; 23,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,76; 13,77</t>
+          <t>7,85; 13,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,78; 33,35</t>
+          <t>24,65; 33,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,2; 33,67</t>
+          <t>24,73; 33,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,79; 26,29</t>
+          <t>19,01; 26,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 13,8</t>
+          <t>8,99; 14,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,31; 30,06</t>
+          <t>24,6; 30,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,1; 32,81</t>
+          <t>26,3; 32,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,67; 24,24</t>
+          <t>18,62; 24,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,18</t>
+          <t>9,02; 13,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,86; 30,13</t>
+          <t>27,03; 30,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,36; 34,67</t>
+          <t>31,24; 34,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,71; 26,8</t>
+          <t>23,65; 26,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,2; 38,8</t>
+          <t>11,3; 37,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,32; 38,83</t>
+          <t>35,37; 38,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,0; 40,58</t>
+          <t>37,02; 40,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,23; 28,31</t>
+          <t>25,28; 28,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,44; 14,49</t>
+          <t>10,2; 14,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,63; 34,08</t>
+          <t>31,63; 34,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,78; 37,23</t>
+          <t>34,63; 37,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,95; 27,15</t>
+          <t>24,92; 27,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,97; 27,23</t>
+          <t>11,91; 26,12</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que tienen algún familiar que fuma habitualmente en casa</t>
+          <t>Población que tienen algún familiar que fuma habitualmente en casa (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>182449; 233714</t>
+          <t>181704; 231763</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>215317; 272093</t>
+          <t>218026; 271218</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130115; 174534</t>
+          <t>130415; 173515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37385; 65269</t>
+          <t>38176; 65701</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>340328; 404366</t>
+          <t>340955; 404296</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>385878; 457103</t>
+          <t>390060; 454523</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>163642; 211362</t>
+          <t>160353; 210868</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58531; 84269</t>
+          <t>58306; 84387</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>539692; 618072</t>
+          <t>538590; 618722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>615979; 703952</t>
+          <t>616624; 704497</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>302093; 365128</t>
+          <t>304141; 371382</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>103308; 141199</t>
+          <t>102956; 140257</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>495354; 575660</t>
+          <t>495342; 574113</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>660171; 743567</t>
+          <t>658286; 747103</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>503376; 582215</t>
+          <t>503258; 584063</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>241583; 925979</t>
+          <t>242450; 1002452</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>610960; 690372</t>
+          <t>607479; 685625</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>717906; 798965</t>
+          <t>715940; 797238</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>536777; 618934</t>
+          <t>534892; 616659</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>212686; 343826</t>
+          <t>205970; 345810</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1125008; 1240125</t>
+          <t>1131579; 1238091</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1402481; 1520213</t>
+          <t>1398218; 1525386</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1062722; 1180415</t>
+          <t>1055130; 1176130</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>525911; 1448283</t>
+          <t>535083; 1456875</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>113326; 156305</t>
+          <t>113857; 153427</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>112875; 154922</t>
+          <t>113649; 155993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80667; 121180</t>
+          <t>81106; 117640</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47051; 83537</t>
+          <t>47593; 84385</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>109107; 146844</t>
+          <t>108526; 146219</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>104640; 145599</t>
+          <t>106905; 146173</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95128; 133059</t>
+          <t>96212; 134484</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55987; 85967</t>
+          <t>55991; 87296</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>232522; 287535</t>
+          <t>235315; 293663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>230407; 289621</t>
+          <t>232179; 290567</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>186283; 241839</t>
+          <t>185805; 240486</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>112321; 162033</t>
+          <t>110960; 159831</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>819766; 919521</t>
+          <t>824973; 926295</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1026583; 1134798</t>
+          <t>1022590; 1134847</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>743215; 840011</t>
+          <t>741354; 843002</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>354371; 1227196</t>
+          <t>357400; 1189959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1092109; 1200621</t>
+          <t>1093745; 1202815</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1242782; 1363079</t>
+          <t>1243290; 1361347</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>825569; 926473</t>
+          <t>827116; 929912</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>350612; 486463</t>
+          <t>342393; 478885</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1943595; 2094258</t>
+          <t>1943490; 2096193</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2306889; 2469336</t>
+          <t>2296987; 2459305</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1598283; 1739216</t>
+          <t>1596195; 1745470</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>780402; 1775609</t>
+          <t>776863; 1703656</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P26-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P26-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,47; 24,84</t>
+          <t>19,36; 24,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,54; 29,28</t>
+          <t>23,13; 29,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,24; 25,6</t>
+          <t>19,17; 25,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,75; 15,06</t>
+          <t>9,32; 15,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,07; 35,65</t>
+          <t>30,27; 35,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,95; 37,23</t>
+          <t>31,53; 37,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,25; 24,0</t>
+          <t>18,43; 24,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,43; 13,65</t>
+          <t>9,15; 13,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,06; 29,93</t>
+          <t>26,12; 29,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,72; 32,81</t>
+          <t>28,85; 33,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,54; 23,86</t>
+          <t>19,59; 23,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,76; 13,3</t>
+          <t>9,79; 13,17</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,91; 35,82</t>
+          <t>30,98; 35,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,71; 39,39</t>
+          <t>34,86; 39,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,61; 29,73</t>
+          <t>25,73; 29,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,43; 47,28</t>
+          <t>10,06; 13,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,02; 45,16</t>
+          <t>40,36; 45,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,98; 46,75</t>
+          <t>41,96; 46,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,34; 32,67</t>
+          <t>28,52; 33,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 16,33</t>
+          <t>14,09; 17,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,26; 39,67</t>
+          <t>36,24; 39,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38,82; 42,35</t>
+          <t>38,74; 42,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,39; 30,53</t>
+          <t>27,53; 30,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,63; 34,38</t>
+          <t>12,47; 14,85</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,06; 29,72</t>
+          <t>21,96; 29,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,23; 34,64</t>
+          <t>25,35; 34,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,5; 23,93</t>
+          <t>16,61; 24,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,85; 13,91</t>
+          <t>7,62; 13,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,65; 33,21</t>
+          <t>24,35; 33,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,73; 33,81</t>
+          <t>24,69; 34,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,01; 26,57</t>
+          <t>18,5; 26,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 14,01</t>
+          <t>9,02; 13,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,6; 30,7</t>
+          <t>24,41; 30,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,3; 32,92</t>
+          <t>25,83; 32,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,62; 24,1</t>
+          <t>18,81; 24,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,02; 13,0</t>
+          <t>8,92; 12,47</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,03; 30,35</t>
+          <t>26,83; 30,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,24; 34,67</t>
+          <t>31,09; 34,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 26,9</t>
+          <t>23,76; 26,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,3; 37,62</t>
+          <t>10,12; 12,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,37; 38,9</t>
+          <t>35,5; 38,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,02; 40,53</t>
+          <t>36,92; 40,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,28; 28,42</t>
+          <t>25,24; 28,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,2; 14,26</t>
+          <t>12,63; 14,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,63; 34,12</t>
+          <t>31,74; 34,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,63; 37,08</t>
+          <t>34,75; 37,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,92; 27,25</t>
+          <t>24,93; 27,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,91; 26,12</t>
+          <t>11,77; 13,44</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50993</t>
+          <t>58062</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69797</t>
+          <t>74251</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>120790</t>
+          <t>132313</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>181704; 231763</t>
+          <t>180658; 232029</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>218026; 271218</t>
+          <t>214264; 270357</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130415; 173515</t>
+          <t>129918; 173397</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38176; 65701</t>
+          <t>45416; 75207</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>340955; 404296</t>
+          <t>343205; 403119</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>390060; 454523</t>
+          <t>384994; 454144</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>160353; 210868</t>
+          <t>161921; 214293</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58306; 84387</t>
+          <t>61839; 88597</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>538590; 618722</t>
+          <t>539914; 618921</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>616624; 704497</t>
+          <t>619482; 709789</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>304141; 371382</t>
+          <t>304879; 371275</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>102956; 140257</t>
+          <t>113912; 153230</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>470434</t>
+          <t>240272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>292136</t>
+          <t>315514</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>762570</t>
+          <t>555786</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>495342; 574113</t>
+          <t>496519; 576650</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>658286; 747103</t>
+          <t>661129; 745327</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>503258; 584063</t>
+          <t>505551; 582587</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>242450; 1002452</t>
+          <t>205161; 279261</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>607479; 685625</t>
+          <t>612672; 689046</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>715940; 797238</t>
+          <t>715510; 799383</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>534892; 616659</t>
+          <t>538442; 622844</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>205970; 345810</t>
+          <t>286687; 349368</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1131579; 1238091</t>
+          <t>1130939; 1239193</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1398218; 1525386</t>
+          <t>1395414; 1516359</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1055130; 1176130</t>
+          <t>1060568; 1174599</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>535083; 1456875</t>
+          <t>507959; 604809</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64256</t>
+          <t>67466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>70237</t>
+          <t>76425</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>134493</t>
+          <t>143891</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>113857; 153427</t>
+          <t>113364; 153983</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>113649; 155993</t>
+          <t>114178; 154991</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81106; 117640</t>
+          <t>81651; 122209</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47593; 84385</t>
+          <t>50501; 88821</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>108526; 146219</t>
+          <t>107228; 147732</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>106905; 146173</t>
+          <t>106731; 147839</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96212; 134484</t>
+          <t>93646; 133684</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55991; 87296</t>
+          <t>62612; 93385</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>235315; 293663</t>
+          <t>233487; 290253</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>232179; 290567</t>
+          <t>228009; 286127</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185805; 240486</t>
+          <t>187673; 241339</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>110960; 159831</t>
+          <t>121079; 169168</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>585683</t>
+          <t>365800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>432170</t>
+          <t>466190</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1017853</t>
+          <t>831991</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>824973; 926295</t>
+          <t>818869; 923660</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1022590; 1134847</t>
+          <t>1017679; 1129215</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>741354; 843002</t>
+          <t>744787; 844381</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>357400; 1189959</t>
+          <t>322749; 408078</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1093745; 1202815</t>
+          <t>1097897; 1201372</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1243290; 1361347</t>
+          <t>1239886; 1361468</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>827116; 929912</t>
+          <t>825799; 925322</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>342393; 478885</t>
+          <t>430079; 505565</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1943490; 2096193</t>
+          <t>1949927; 2091256</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2296987; 2459305</t>
+          <t>2304699; 2466671</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1596195; 1745470</t>
+          <t>1597379; 1736393</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>776863; 1703656</t>
+          <t>775882; 886308</t>
         </is>
       </c>
     </row>
